--- a/타기관벤치마킹_20260807.xlsx
+++ b/타기관벤치마킹_20260807.xlsx
@@ -469,7 +469,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/frt/bbs/type013/commonSelectBoardArticle.do;jsessionid=tstRgKL_IR2D-dOVEt5Zb5QoVIozzsbsf23_D8NY.node20?bbsId=BBSMSTR_000000000006&amp;nttId=128313</t>
+          <t>https://www.mois.go.kr/frt/bbs/type013/commonSelectBoardArticle.do;jsessionid=znoXSmre_m-XpiXdcKbJ9Jxb9YMYcH1QerZD7tUK.node40?bbsId=BBSMSTR_000000000006&amp;nttId=128313</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/frt/bbs/type013/commonSelectBoardArticle.do;jsessionid=gRP6C8XgFZiaOfIR2_aNpsJMJfchQTtP8qV64Ml8.node40?bbsId=BBSMSTR_000000000006&amp;nttId=128214</t>
+          <t>https://www.mois.go.kr/frt/bbs/type013/commonSelectBoardArticle.do;jsessionid=0E4HkFAStbVAXXgjeIZVDgNJTAgnx3Bpn7u4fchL.node30?bbsId=BBSMSTR_000000000006&amp;nttId=128214</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/frt/bbs/type013/commonSelectBoardArticle.do;jsessionid=A83sHsg03bwguCOFnALuALyH7SRfWHbkvYQfDbMq.node20?bbsId=BBSMSTR_000000000006&amp;nttId=128199</t>
+          <t>https://www.mois.go.kr/frt/bbs/type013/commonSelectBoardArticle.do;jsessionid=yXRVI_KyUH9PBv0BBSGAEB-jrdCVKKP4TVXnFR68.node20?bbsId=BBSMSTR_000000000006&amp;nttId=128199</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/frt/bbs/type013/commonSelectBoardArticle.do;jsessionid=A83sHsg03bwguCOFnALuALyH7SRfWHbkvYQfDbMq.node20?bbsId=BBSMSTR_000000000006&amp;nttId=128194</t>
+          <t>https://www.mois.go.kr/frt/bbs/type013/commonSelectBoardArticle.do;jsessionid=yXRVI_KyUH9PBv0BBSGAEB-jrdCVKKP4TVXnFR68.node20?bbsId=BBSMSTR_000000000006&amp;nttId=128194</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/frt/bbs/type013/commonSelectBoardArticle.do;jsessionid=tstRgKL_IR2D-dOVEt5Zb5QoVIozzsbsf23_D8NY.node20?bbsId=BBSMSTR_000000000006&amp;nttId=128313</t>
+          <t>https://www.mois.go.kr/frt/bbs/type013/commonSelectBoardArticle.do;jsessionid=znoXSmre_m-XpiXdcKbJ9Jxb9YMYcH1QerZD7tUK.node40?bbsId=BBSMSTR_000000000006&amp;nttId=128313</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/frt/bbs/type013/commonSelectBoardArticle.do;jsessionid=gRP6C8XgFZiaOfIR2_aNpsJMJfchQTtP8qV64Ml8.node40?bbsId=BBSMSTR_000000000006&amp;nttId=128214</t>
+          <t>https://www.mois.go.kr/frt/bbs/type013/commonSelectBoardArticle.do;jsessionid=0E4HkFAStbVAXXgjeIZVDgNJTAgnx3Bpn7u4fchL.node30?bbsId=BBSMSTR_000000000006&amp;nttId=128214</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/frt/bbs/type013/commonSelectBoardArticle.do;jsessionid=A83sHsg03bwguCOFnALuALyH7SRfWHbkvYQfDbMq.node20?bbsId=BBSMSTR_000000000006&amp;nttId=128199</t>
+          <t>https://www.mois.go.kr/frt/bbs/type013/commonSelectBoardArticle.do;jsessionid=yXRVI_KyUH9PBv0BBSGAEB-jrdCVKKP4TVXnFR68.node20?bbsId=BBSMSTR_000000000006&amp;nttId=128199</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/frt/bbs/type013/commonSelectBoardArticle.do;jsessionid=A83sHsg03bwguCOFnALuALyH7SRfWHbkvYQfDbMq.node20?bbsId=BBSMSTR_000000000006&amp;nttId=128194</t>
+          <t>https://www.mois.go.kr/frt/bbs/type013/commonSelectBoardArticle.do;jsessionid=yXRVI_KyUH9PBv0BBSGAEB-jrdCVKKP4TVXnFR68.node20?bbsId=BBSMSTR_000000000006&amp;nttId=128194</t>
         </is>
       </c>
     </row>
